--- a/data/trending_integrated_20261019_11.xlsx
+++ b/data/trending_integrated_20261019_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20181467308</v>
+        <v>20206839528</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -619,14 +619,14 @@
         <v>890</v>
       </c>
       <c r="R2" t="n">
-        <v>821000</v>
+        <v>918000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 단독 보도. 4월부터 납품 시작 확인.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 관련 단독 보도 확인. 4월부터 납품 시작, 이번 호재로 상승 흐름 예상.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관', '단독']</t>
+          <t>['스페이스X', '납품', '강관']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9480</v>
+        <v>9410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.19%</t>
+          <t>'+11.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>18767795875</v>
+        <v>19126335450</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -711,10 +711,10 @@
         <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>-327000</v>
+        <v>-259000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170900</v>
+        <v>170500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.21%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>373304543850</v>
+        <v>382907902050</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -803,10 +803,10 @@
         <v>71000</v>
       </c>
       <c r="R4" t="n">
-        <v>133000</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
-        <v>-31000</v>
+        <v>-30000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15210</v>
+        <v>15090</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H5" t="n">
         <v>0.06</v>
@@ -886,7 +886,7 @@
         <v>0.11</v>
       </c>
       <c r="O5" t="n">
-        <v>25044788220</v>
+        <v>25389324890</v>
       </c>
       <c r="P5" t="n">
         <v>30800</v>
@@ -895,7 +895,7 @@
         <v>9810</v>
       </c>
       <c r="R5" t="n">
-        <v>31000</v>
+        <v>23000</v>
       </c>
       <c r="S5" t="n">
         <v>1000</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>216000</v>
+        <v>214750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G6" t="n">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="H6" t="n">
         <v>45.99</v>
@@ -978,7 +978,7 @@
         <v>45.98</v>
       </c>
       <c r="O6" t="n">
-        <v>1530892577000</v>
+        <v>1581979176000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -987,14 +987,14 @@
         <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>1113000</v>
+        <v>1715000</v>
       </c>
       <c r="S6" t="n">
-        <v>504000</v>
+        <v>573000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>일부 투자자들은 정치적 이슈와 연관 지어 시장을 비판하며 매수를 독려하나, 객관적인 근거는 부족함.</t>
+          <t>삼성전자 주가 하락에 대한 정치적 책임론과 외인 매수세 관련 언급. 일부 투자자는 주가 하락에 대한 불만을 표현하며 시장 떠날 의사 표명.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['영업이익', '매수', '주가']</t>
+          <t>['외인', '주가', '영업이익']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H7" t="n">
         <v>9.699999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>17373884300</v>
+        <v>17771851290</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1079,10 +1079,10 @@
         <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>33000</v>
+        <v>32000</v>
       </c>
       <c r="S7" t="n">
-        <v>-2000</v>
+        <v>-29000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1115,123 +1115,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1238000</v>
+        <v>8770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.03</v>
+        <v>1.02</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>507</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>1391</v>
+        <v>198</v>
       </c>
       <c r="H8" t="n">
-        <v>48.82</v>
+        <v>1.74</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1272000</v>
+        <v>9010</v>
       </c>
       <c r="K8" t="n">
-        <v>1212000</v>
+        <v>8810</v>
       </c>
       <c r="L8" t="n">
-        <v>1264000</v>
+        <v>9500</v>
       </c>
       <c r="M8" t="n">
-        <v>1208000</v>
+        <v>8510</v>
       </c>
       <c r="N8" t="n">
-        <v>48.85</v>
+        <v>0.72</v>
       </c>
       <c r="O8" t="n">
-        <v>2022657154500</v>
+        <v>94631237095</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>9500</v>
       </c>
       <c r="Q8" t="n">
-        <v>465500</v>
+        <v>2270</v>
       </c>
       <c r="R8" t="n">
-        <v>73000</v>
+        <v>-181000</v>
       </c>
       <c r="S8" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>솔리다임 우회상장 철회 요구가 거세며, 이에 대한 부정적인 전망이 지배적임.</t>
+          <t>HT로보틱스, 로봇주 강세 속 주가 변동성 관측. 연말 주도주 가능성 탐색.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '철회']</t>
+          <t>['로봇주', '주도주', '변동성']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17740</v>
+        <v>1231000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.59%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>513</v>
       </c>
       <c r="G9" t="n">
-        <v>138</v>
+        <v>1530</v>
       </c>
       <c r="H9" t="n">
-        <v>27.85</v>
+        <v>48.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,130 +1239,130 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18400</v>
+        <v>1272000</v>
       </c>
       <c r="K9" t="n">
-        <v>17690</v>
+        <v>1212000</v>
       </c>
       <c r="L9" t="n">
-        <v>17950</v>
+        <v>1264000</v>
       </c>
       <c r="M9" t="n">
-        <v>17670</v>
+        <v>1208000</v>
       </c>
       <c r="N9" t="n">
-        <v>27.77</v>
+        <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>22697134950</v>
+        <v>2077269310000</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>17210</v>
+        <v>465500</v>
       </c>
       <c r="R9" t="n">
-        <v>-189000</v>
+        <v>54000</v>
       </c>
       <c r="S9" t="n">
-        <v>-4000</v>
+        <v>59000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
+          <t>SK하이닉스, 솔리다임 상장 관련 논란으로 부정적 여론 형성. 주주들은 솔리다임 상장 철회를 요구하며 경영진에 대한 비판 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['조선주', '공매도', '목표가']</t>
+          <t>['솔리다임', '상장', '쪼개기']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8650</v>
+        <v>17740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-3.59%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.02</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H10" t="n">
-        <v>1.74</v>
+        <v>27.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>9010</v>
+        <v>18400</v>
       </c>
       <c r="K10" t="n">
-        <v>8810</v>
+        <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>9500</v>
+        <v>17950</v>
       </c>
       <c r="M10" t="n">
-        <v>8510</v>
+        <v>17670</v>
       </c>
       <c r="N10" t="n">
-        <v>0.72</v>
+        <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>92691363485</v>
+        <v>23785210915</v>
       </c>
       <c r="P10" t="n">
-        <v>9500</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>2270</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-197000</v>
+        <v>-481000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 강세 속 주가 변동성 관측. 연말 주도주 가능성 탐색.</t>
+          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇주', '주도주', '변동성']</t>
+          <t>['조선주', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.68%</t>
+          <t>'-4.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9123910810</v>
+        <v>9466605143</v>
       </c>
       <c r="P11" t="n">
         <v>1950</v>
@@ -1447,7 +1447,7 @@
         <v>192</v>
       </c>
       <c r="R11" t="n">
-        <v>-264000</v>
+        <v>-321000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14100</v>
+        <v>13980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.06%</t>
+          <t>'-6.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>33474214990</v>
+        <v>34117283610</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>
@@ -1539,7 +1539,7 @@
         <v>13610</v>
       </c>
       <c r="R12" t="n">
-        <v>29000</v>
+        <v>35000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>

--- a/data/trending_integrated_20261019_11.xlsx
+++ b/data/trending_integrated_20261019_11.xlsx
@@ -581,10 +581,10 @@
         <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20206839528</v>
+        <v>20249946956</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9410</v>
+        <v>9540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.36%</t>
+          <t>'+12.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>19126335450</v>
+        <v>19672805760</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170500</v>
+        <v>170800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,7 +765,7 @@
         <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
         <v>204</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>382907902050</v>
+        <v>391930730500</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15090</v>
+        <v>15210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>52</v>
@@ -886,7 +886,7 @@
         <v>0.11</v>
       </c>
       <c r="O5" t="n">
-        <v>25389324890</v>
+        <v>25642063650</v>
       </c>
       <c r="P5" t="n">
         <v>30800</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>214750</v>
+        <v>14720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>496</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>1433</v>
+        <v>128</v>
       </c>
       <c r="H6" t="n">
-        <v>45.99</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>215500</v>
+        <v>14730</v>
       </c>
       <c r="K6" t="n">
-        <v>207000</v>
+        <v>14500</v>
       </c>
       <c r="L6" t="n">
-        <v>219500</v>
+        <v>14910</v>
       </c>
       <c r="M6" t="n">
-        <v>206500</v>
+        <v>14120</v>
       </c>
       <c r="N6" t="n">
-        <v>45.98</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1581979176000</v>
+        <v>20303351045</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>1715000</v>
+        <v>32000</v>
       </c>
       <c r="S6" t="n">
-        <v>573000</v>
+        <v>-29000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 주가 하락에 대한 정치적 책임론과 외인 매수세 관련 언급. 일부 투자자는 주가 하락에 대한 불만을 표현하며 시장 떠날 의사 표명.</t>
+          <t>대우건설, 주가 하락 및 반등 시도. 정치권 정책 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인', '주가', '영업이익']</t>
+          <t>['대우건설', '주가 하락', '정치권']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,82 +1011,82 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14620</v>
+        <v>8990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="H7" t="n">
-        <v>9.699999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14730</v>
+        <v>9010</v>
       </c>
       <c r="K7" t="n">
-        <v>14500</v>
+        <v>8810</v>
       </c>
       <c r="L7" t="n">
-        <v>14840</v>
+        <v>9500</v>
       </c>
       <c r="M7" t="n">
-        <v>14120</v>
+        <v>8510</v>
       </c>
       <c r="N7" t="n">
-        <v>9.779999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="O7" t="n">
-        <v>17771851290</v>
+        <v>99044255075</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>9500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>2270</v>
       </c>
       <c r="R7" t="n">
-        <v>32000</v>
+        <v>-181000</v>
       </c>
       <c r="S7" t="n">
-        <v>-29000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설, 주가 하락 및 반등 시도. 정치권 정책 관련 언급 다수.</t>
+          <t>HT로보틱스, 로봇주 강세 속 주가 변동성 관측. 연말 주도주 가능성 탐색.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['대우건설', '주가 하락', '정치권']</t>
+          <t>['로봇주', '주도주', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,99 +1108,99 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8770</v>
+        <v>215000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.02</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>497</v>
       </c>
       <c r="G8" t="n">
-        <v>198</v>
+        <v>1498</v>
       </c>
       <c r="H8" t="n">
-        <v>1.74</v>
+        <v>45.99</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9010</v>
+        <v>215500</v>
       </c>
       <c r="K8" t="n">
-        <v>8810</v>
+        <v>207000</v>
       </c>
       <c r="L8" t="n">
-        <v>9500</v>
+        <v>219500</v>
       </c>
       <c r="M8" t="n">
-        <v>8510</v>
+        <v>206500</v>
       </c>
       <c r="N8" t="n">
-        <v>0.72</v>
+        <v>45.98</v>
       </c>
       <c r="O8" t="n">
-        <v>94631237095</v>
+        <v>1638906613500</v>
       </c>
       <c r="P8" t="n">
-        <v>9500</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>2270</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>-181000</v>
+        <v>1715000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>573000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 강세 속 주가 변동성 관측. 연말 주도주 가능성 탐색.</t>
+          <t>시장 참여자들은 이재명 관련 정치적 요인과 일부 경영진의 행태에 대한 불만을 표출하고 있으며, 개별 투자자들의 단기 매매 경험이 혼재되어 있다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇주', '주도주', '변동성']</t>
+          <t>['영업이익', '배당', '주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1231000</v>
+        <v>1235000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="G9" t="n">
-        <v>1530</v>
+        <v>1572</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2077269310000</v>
+        <v>2128809833500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 상장 관련 논란으로 부정적 여론 형성. 주주들은 솔리다임 상장 철회를 요구하며 경영진에 대한 비판 제기.</t>
+          <t>솔리다임 상장 철회 요구와 최태원 회장 관련 비판이 주를 이루며, 회사 경영 및 분할 상장에 대한 강한 부정적 인식이 나타난다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '쪼개기']</t>
+          <t>['솔리다임', '최태원', '상장']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17740</v>
+        <v>17805</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.59%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>23785210915</v>
+        <v>24694808640</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-4.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9466605143</v>
+        <v>9747321525</v>
       </c>
       <c r="P11" t="n">
         <v>1950</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13980</v>
+        <v>14070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.86%</t>
+          <t>'-6.26%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>34117283610</v>
+        <v>34514734885</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>

--- a/data/trending_integrated_20261019_11.xlsx
+++ b/data/trending_integrated_20261019_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20249946956</v>
+        <v>20304266056</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 관련 단독 보도 확인. 4월부터 납품 시작, 이번 호재로 상승 흐름 예상.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 계약 체결. 4월부터 납품 시작. 주가 전고점 4042원 도달 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '납품', '강관']</t>
+          <t>['KBI동양철관', '스페이스X', '강관 공급']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9540</v>
+        <v>9560</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.90%</t>
+          <t>'+13.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
         <v>140</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>19672805760</v>
+        <v>20137941960</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -762,13 +762,13 @@
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>391930730500</v>
+        <v>398592728300</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15210</v>
+        <v>15130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>0.11</v>
       </c>
       <c r="O5" t="n">
-        <v>25642063650</v>
+        <v>25719927860</v>
       </c>
       <c r="P5" t="n">
         <v>30800</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14720</v>
+        <v>14730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>20303351045</v>
+        <v>20627778810</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 주가 하락 및 반등 시도. 정치권 정책 관련 언급 다수.</t>
+          <t>대우건설, 민주당 정책 및 이재명 대통령 관련 정치적 언급. 대차 잔고 및 주가 조작 의혹 제기. 수주 시 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대우건설', '주가 하락', '정치권']</t>
+          <t>['대우건설', '이재명', '주가 조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8990</v>
+        <v>9010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H7" t="n">
         <v>1.74</v>
@@ -1070,7 +1070,7 @@
         <v>0.72</v>
       </c>
       <c r="O7" t="n">
-        <v>99044255075</v>
+        <v>103579728975</v>
       </c>
       <c r="P7" t="n">
         <v>9500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 강세 속 주가 변동성 관측. 연말 주도주 가능성 탐색.</t>
+          <t>HT로보틱스, 종목 분석글 등장 후 급락 예상. 로봇주 관련 기대감 있으나, 개인 투자자 손실 경험 다수.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['로봇주', '주도주', '변동성']</t>
+          <t>['HT로보틱스', '로봇주', '분석글']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="G8" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="H8" t="n">
         <v>45.99</v>
@@ -1162,7 +1162,7 @@
         <v>45.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1638906613500</v>
+        <v>1690215639500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>시장 참여자들은 이재명 관련 정치적 요인과 일부 경영진의 행태에 대한 불만을 표출하고 있으며, 개별 투자자들의 단기 매매 경험이 혼재되어 있다.</t>
+          <t>삼성전자, 이재명 관련 정치적 언급 및 주가 조작 의혹 제기. 영업이익 및 배당 관련 기대감 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '배당', '주가']</t>
+          <t>['삼성전자', '이재명', '영업이익']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="G9" t="n">
-        <v>1572</v>
+        <v>1670</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2128809833500</v>
+        <v>2174928275500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 요구와 최태원 회장 관련 비판이 주를 이루며, 회사 경영 및 분할 상장에 대한 강한 부정적 인식이 나타난다.</t>
+          <t>SK하이닉스, 솔리다임 관련 논란 및 최태원 회장 사생활 문제 제기. 주주 손실 및 회사 경영 투명성 의혹.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원', '상장']</t>
+          <t>['SK하이닉스', '솔리다임', '최태원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17805</v>
+        <v>1220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>155</v>
+        <v>50</v>
       </c>
       <c r="H10" t="n">
-        <v>27.85</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18400</v>
+        <v>1261</v>
       </c>
       <c r="K10" t="n">
-        <v>17690</v>
+        <v>1301</v>
       </c>
       <c r="L10" t="n">
-        <v>17950</v>
+        <v>1339</v>
       </c>
       <c r="M10" t="n">
-        <v>17670</v>
+        <v>1145</v>
       </c>
       <c r="N10" t="n">
-        <v>27.77</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24694808640</v>
+        <v>9929609015</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>1950</v>
       </c>
       <c r="Q10" t="n">
-        <v>17210</v>
+        <v>192</v>
       </c>
       <c r="R10" t="n">
-        <v>-481000</v>
+        <v>-321000</v>
       </c>
       <c r="S10" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
+          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선주', '공매도', '목표가']</t>
+          <t>['데이터센터', 'AI', '성장성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>317240</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1202</v>
+        <v>17780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.68%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>27.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1261</v>
+        <v>18400</v>
       </c>
       <c r="K11" t="n">
-        <v>1301</v>
+        <v>17690</v>
       </c>
       <c r="L11" t="n">
-        <v>1339</v>
+        <v>17950</v>
       </c>
       <c r="M11" t="n">
-        <v>1145</v>
+        <v>17670</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>27.77</v>
       </c>
       <c r="O11" t="n">
-        <v>9747321525</v>
+        <v>25230345220</v>
       </c>
       <c r="P11" t="n">
-        <v>1950</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>192</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>-321000</v>
+        <v>-481000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
+          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['데이터센터', 'AI', '성장성']</t>
+          <t>['조선주', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>317240</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14070</v>
+        <v>14050</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.26%</t>
+          <t>'-6.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>34514734885</v>
+        <v>34720131475</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>

--- a/data/trending_integrated_20261019_11.xlsx
+++ b/data/trending_integrated_20261019_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20304266056</v>
+        <v>20320127408</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 계약 체결. 4월부터 납품 시작. 주가 전고점 4042원 도달 기대.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 이슈 부각. 주가는 기대감 및 상징성 반영하며 전고점 돌파 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['KBI동양철관', '스페이스X', '강관 공급']</t>
+          <t>['스페이스X', '납품', '강관']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9560</v>
+        <v>9580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.14%</t>
+          <t>'+13.37%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
         <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>20137941960</v>
+        <v>20763335645</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170800</v>
+        <v>171400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>398592728300</v>
+        <v>406257855500</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15130</v>
+        <v>15050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.20%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>52</v>
@@ -886,7 +886,7 @@
         <v>0.11</v>
       </c>
       <c r="O5" t="n">
-        <v>25719927860</v>
+        <v>25843306370</v>
       </c>
       <c r="P5" t="n">
         <v>30800</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14730</v>
+        <v>14810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
         <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>20627778810</v>
+        <v>21095602935</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 민주당 정책 및 이재명 대통령 관련 정치적 언급. 대차 잔고 및 주가 조작 의혹 제기. 수주 시 하락 가능성 언급.</t>
+          <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대우건설', '이재명', '주가 조작']</t>
+          <t>['뱅크런', '주가조작', '이재명']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9010</v>
+        <v>216000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>501</v>
       </c>
       <c r="G7" t="n">
-        <v>195</v>
+        <v>1489</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>45.99</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9010</v>
+        <v>215500</v>
       </c>
       <c r="K7" t="n">
-        <v>8810</v>
+        <v>207000</v>
       </c>
       <c r="L7" t="n">
-        <v>9500</v>
+        <v>219500</v>
       </c>
       <c r="M7" t="n">
-        <v>8510</v>
+        <v>206500</v>
       </c>
       <c r="N7" t="n">
-        <v>0.72</v>
+        <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>103579728975</v>
+        <v>1727337898500</v>
       </c>
       <c r="P7" t="n">
-        <v>9500</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2270</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-181000</v>
+        <v>1715000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>573000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HT로보틱스, 종목 분석글 등장 후 급락 예상. 로봇주 관련 기대감 있으나, 개인 투자자 손실 경험 다수.</t>
+          <t>삼성전자, 긍정적/부정적 의견 혼재. 일부 투자자는 실적 및 배당 기대감 표출하나, 정치적 이슈 언급 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['HT로보틱스', '로봇주', '분석글']</t>
+          <t>['영업이익', '배당', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>215000</v>
+        <v>9010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>1.02</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>502</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>1445</v>
+        <v>205</v>
       </c>
       <c r="H8" t="n">
-        <v>45.99</v>
+        <v>1.74</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>215500</v>
+        <v>9010</v>
       </c>
       <c r="K8" t="n">
-        <v>207000</v>
+        <v>8810</v>
       </c>
       <c r="L8" t="n">
-        <v>219500</v>
+        <v>9500</v>
       </c>
       <c r="M8" t="n">
-        <v>206500</v>
+        <v>8510</v>
       </c>
       <c r="N8" t="n">
-        <v>45.98</v>
+        <v>0.72</v>
       </c>
       <c r="O8" t="n">
-        <v>1690215639500</v>
+        <v>106482843030</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>9500</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>2270</v>
       </c>
       <c r="R8" t="n">
-        <v>1715000</v>
+        <v>-181000</v>
       </c>
       <c r="S8" t="n">
-        <v>573000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 이재명 관련 정치적 언급 및 주가 조작 의혹 제기. 영업이익 및 배당 관련 기대감 존재.</t>
+          <t>HT로보틱스, 시장 전반의 부정적 심리 속에서 로봇주에 대한 긍정적 전망 일부 존재. 분석글 등장 시 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성전자', '이재명', '영업이익']</t>
+          <t>['로봇주', '분석글', '급락']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1235000</v>
+        <v>1246000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G9" t="n">
-        <v>1670</v>
+        <v>1714</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2174928275500</v>
+        <v>2240923399000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 관련 논란 및 최태원 회장 사생활 문제 제기. 주주 손실 및 회사 경영 투명성 의혹.</t>
+          <t>SK하이닉스, 솔리다임 상장 이슈로 인한 부정적 여론 형성. 경영진 사생활 문제 및 주식 쪼개기 비판.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '솔리다임', '최태원']</t>
+          <t>['솔리다임', '상장', '최태원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-3.01%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
         <v>19</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>9929609015</v>
+        <v>10198380157</v>
       </c>
       <c r="P10" t="n">
         <v>1950</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17780</v>
+        <v>17790</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.37%</t>
+          <t>'-3.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H11" t="n">
         <v>27.85</v>
@@ -1438,7 +1438,7 @@
         <v>27.77</v>
       </c>
       <c r="O11" t="n">
-        <v>25230345220</v>
+        <v>26123328395</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14050</v>
+        <v>14100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.40%</t>
+          <t>'-6.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>34720131475</v>
+        <v>34930085945</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>

--- a/data/trending_integrated_20261019_11.xlsx
+++ b/data/trending_integrated_20261019_11.xlsx
@@ -584,7 +584,7 @@
         <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20320127408</v>
+        <v>20336619788</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 이슈 부각. 주가는 기대감 및 상징성 반영하며 전고점 돌파 기대감 형성.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 공급 뉴스. 4월부터 납품 시작, 전고점 돌파 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '납품', '강관']</t>
+          <t>['스페이스X', '강관', '납품']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9580</v>
+        <v>9490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.37%</t>
+          <t>'+12.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>20763335645</v>
+        <v>21131713980</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171400</v>
+        <v>171100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>406257855500</v>
+        <v>414432661500</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15050</v>
+        <v>15130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H5" t="n">
         <v>0.06</v>
@@ -886,7 +886,7 @@
         <v>0.11</v>
       </c>
       <c r="O5" t="n">
-        <v>25843306370</v>
+        <v>26011295900</v>
       </c>
       <c r="P5" t="n">
         <v>30800</v>
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14810</v>
+        <v>9060</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'+0.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="H6" t="n">
-        <v>9.699999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14730</v>
+        <v>9010</v>
       </c>
       <c r="K6" t="n">
-        <v>14500</v>
+        <v>8810</v>
       </c>
       <c r="L6" t="n">
-        <v>14910</v>
+        <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>14120</v>
+        <v>8510</v>
       </c>
       <c r="N6" t="n">
-        <v>9.779999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>21095602935</v>
+        <v>107877278555</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>9500</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>2270</v>
       </c>
       <c r="R6" t="n">
-        <v>32000</v>
+        <v>-181000</v>
       </c>
       <c r="S6" t="n">
-        <v>-29000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
+          <t>HT로보틱스, 로봇주 관련 토론 활발. 개인 투자자들의 기대와 손실 경험 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뱅크런', '주가조작', '이재명']</t>
+          <t>['로봇주', '분석글', '손실']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216000</v>
+        <v>14780</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>501</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>1489</v>
+        <v>163</v>
       </c>
       <c r="H7" t="n">
-        <v>45.99</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>215500</v>
+        <v>14730</v>
       </c>
       <c r="K7" t="n">
-        <v>207000</v>
+        <v>14500</v>
       </c>
       <c r="L7" t="n">
-        <v>219500</v>
+        <v>14910</v>
       </c>
       <c r="M7" t="n">
-        <v>206500</v>
+        <v>14120</v>
       </c>
       <c r="N7" t="n">
-        <v>45.98</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1727337898500</v>
+        <v>21697509825</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>1715000</v>
+        <v>32000</v>
       </c>
       <c r="S7" t="n">
-        <v>573000</v>
+        <v>-29000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 긍정적/부정적 의견 혼재. 일부 투자자는 실적 및 배당 기대감 표출하나, 정치적 이슈 언급 및 주가 조작 의혹 제기.</t>
+          <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '배당', '주가조작']</t>
+          <t>['뱅크런', '주가조작', '이재명']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,18 +1108,18 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9010</v>
+        <v>215500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1127,58 +1127,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.02</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>501</v>
       </c>
       <c r="G8" t="n">
-        <v>205</v>
+        <v>1477</v>
       </c>
       <c r="H8" t="n">
-        <v>1.74</v>
+        <v>45.99</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9010</v>
+        <v>215500</v>
       </c>
       <c r="K8" t="n">
-        <v>8810</v>
+        <v>207000</v>
       </c>
       <c r="L8" t="n">
-        <v>9500</v>
+        <v>219500</v>
       </c>
       <c r="M8" t="n">
-        <v>8510</v>
+        <v>206500</v>
       </c>
       <c r="N8" t="n">
-        <v>0.72</v>
+        <v>45.98</v>
       </c>
       <c r="O8" t="n">
-        <v>106482843030</v>
+        <v>1770721674250</v>
       </c>
       <c r="P8" t="n">
-        <v>9500</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>2270</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>-181000</v>
+        <v>1715000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>573000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HT로보틱스, 시장 전반의 부정적 심리 속에서 로봇주에 대한 긍정적 전망 일부 존재. 분석글 등장 시 급락 가능성 언급.</t>
+          <t>삼성전자, 이재명·이주완 관련 언급 및 주가 관련 불확실성 존재. 일부 투자자 긍정적 언급 있으나 전반적 혼조세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇주', '분석글', '급락']</t>
+          <t>['이재명', '이주완', '주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1246000</v>
+        <v>1249000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="G9" t="n">
-        <v>1714</v>
+        <v>1705</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2240923399000</v>
+        <v>2327964119500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1223</v>
+        <v>17840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.01%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>27.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1261</v>
+        <v>18400</v>
       </c>
       <c r="K10" t="n">
-        <v>1301</v>
+        <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>1339</v>
+        <v>17950</v>
       </c>
       <c r="M10" t="n">
-        <v>1145</v>
+        <v>17670</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>10198380157</v>
+        <v>26773962815</v>
       </c>
       <c r="P10" t="n">
-        <v>1950</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>192</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-321000</v>
+        <v>-481000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
+          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['데이터센터', 'AI', '성장성']</t>
+          <t>['조선주', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>317240</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17790</v>
+        <v>1201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.32%</t>
+          <t>'-4.76%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>46</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="n">
         <v>57</v>
       </c>
-      <c r="F11" t="n">
-        <v>37</v>
-      </c>
-      <c r="G11" t="n">
-        <v>167</v>
-      </c>
       <c r="H11" t="n">
-        <v>27.85</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18400</v>
+        <v>1261</v>
       </c>
       <c r="K11" t="n">
-        <v>17690</v>
+        <v>1301</v>
       </c>
       <c r="L11" t="n">
-        <v>17950</v>
+        <v>1339</v>
       </c>
       <c r="M11" t="n">
-        <v>17670</v>
+        <v>1145</v>
       </c>
       <c r="N11" t="n">
-        <v>27.77</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26123328395</v>
+        <v>10395179541</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>1950</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>192</v>
       </c>
       <c r="R11" t="n">
-        <v>-481000</v>
+        <v>-321000</v>
       </c>
       <c r="S11" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
+          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '공매도', '목표가']</t>
+          <t>['데이터센터', 'AI', '성장성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>317240</t>
         </is>
       </c>
     </row>
@@ -1487,18 +1487,18 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14100</v>
+        <v>14210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.06%</t>
+          <t>'-5.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
         <v>44</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>34930085945</v>
+        <v>35452746035</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>
